--- a/public/files/Data_By_Towns_Index/Camden/Winslow Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Camden/Winslow Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,28 +425,1568 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E1"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Owner Name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BHARUCHA PANKAJ I &amp; ILA P</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>142 LAKESIDE DRIVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-74.8936899</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.7587426</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJp7WjOTQswYkRlH4wBOBN038</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL BHUPESH J &amp; SEJAL B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>40 WAKEFIELD ROAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-74.8958901</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.759301</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJmyuPvzUswYkRdBSP1Ti-yfA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL AKSHIT V &amp; VIPULKUMAR &amp; J</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>111 FENWAY AVENUE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.8901176</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.7530587</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJIxFAljAswYkRym5JjX_CYcU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PATEL AKSHIT V &amp; VIPULKUMAR &amp; J</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>111 FENWAY AVENUE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-74.8901176</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.7530587</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJIxFAljAswYkRym5JjX_CYcU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATEL RANJAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5 WOODVALE COURT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-74.90597289999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.7599683</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJM2UDMkwswYkR0UT9Pq2NPv4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHAH HASMUKHLA V &amp; PREMILABE H</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>77 SENATORS WAY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-74.91441300000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39.773833</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJ2eCRRq8twYkR8K-AFH4X5jU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SHAH HASMUKHLA V &amp; PREMILABE H</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>77 SENATORS WAY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-74.91441300000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.773833</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJ2eCRRq8twYkR8K-AFH4X5jU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEL CHANDRAKANT &amp; SUSHILADEVI ETA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>519 RIGGS AVENUE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-74.9181371</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.7763193</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJc_WJ1KctwYkRQljPzhVwJgk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SHAH SURESH V &amp; KALPANA S</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>542 RIGGS AVENUE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-74.92142059999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.776375</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ChIJc0Cp_QctwYkRZtk_J-LSVdM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PATEL NIRMITA &amp; SHAH SAVAN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4 ENGLISH IVY DRIVE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-74.9698509</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39.7540209</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ChIJ1ZNcDTXTxokRD5eRxpksOPo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PATEL RAJESH &amp; BHAVNA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>100 HARMONY CIRCLE ROAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>-74.9733664</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39.753042</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ChIJrVVAAErTxokRFPq2ZRDbFIc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PATEL NIKUNJ V &amp; PAYAL B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>66 WILDCAT BRANCH DRIVE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>-74.97582210000002</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.7499595</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ChIJFQicGUnTxokRsWbaoFbgT4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PATEL CHANDRAKANT M</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6 RAGAN RIDGE ROAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>-74.9723619</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.7465712</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ChIJLV98PkzTxokRWGy2SC0T3Vk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SHARMA HARISH KUMAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21 RAGAN RIDGE ROAD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-74.9700464</v>
+      </c>
+      <c r="G15" t="n">
+        <v>39.745825</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ChIJjxaF8EzTxokR_KsYJZkMGPk</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MEHTA NEIL A &amp; PRUNA SAMANTHA O</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>47 COACHLIGHT DRIVE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>-74.96942559999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>39.7451188</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ChIJKRfu4UzTxokRuN1nOYIg7aY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SHAH VIRAL H &amp; PATEL DISHA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>114 CARISSA LANE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>-74.9782788</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.7390678</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ChIJExQ4sVDTxokRlzYOFLUWV6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PATEL JAYMIN P &amp; SHRADHABE M</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>139 CISELEY DRIVE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>-74.98082239999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39.7389933</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ChIJcw3LilnTxokRix351-vpOQ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PATEL RAJ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>72 BREARLY DRIVE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>-74.98314049999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>39.7406908</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ChIJ_Z72uFvTxokRXIUqfCZeiPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PATEL PRASHANT B &amp; MONA P</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20 ORLANDO DRIVE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>-74.98941189999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>39.7365533</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ChIJp_UEv1_TxokRbhbAHBHR8yI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RANA JAI B &amp; LACHHIMI K</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13 REVERE WAY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>-74.9884374</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.73330929999999</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ChIJ4XpkWaDUxokRnAqUxk5HrAg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PATEL CHANDRESH J &amp; JAYSHRI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48 CONCORD BLVD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>-74.9867192</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39.7328669</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ChIJvTXg56DUxokRhdvlgYRIIiE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PATEL JAYESH &amp; NILA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7 STONE HOLLOW DRIVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>-74.98551019999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>39.7283416</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ChIJEwej9KPUxokRqXCnQZJozn4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BHATT NEHAL &amp; ET ALS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>103 SUMMERBROOKE COURT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>-74.98502139999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39.7273516</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ChIJvVvceKTUxokREjJzu0bRlto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PATEL TAPAN &amp; KINJAL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>100 SUMMERBROOKE COURT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>-74.98471239999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39.7268756</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ChIJ7U9dh6TUxokR59krXL5DPzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PANDYA REKHABEN J</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>112 SICKLER COURT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>-74.975016</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39.7246044</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ChIJrYOVW67UxokRHai06yw5rT8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SHAH PARTH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>60 HAMPTON GATE DRIVE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>-74.97414379999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>39.716824</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ChIJSajcorbUxokRWY1n1F9Jq3E</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RATHOD ARCHANA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>9 THOUSAND OAK DRIVE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>-74.96363749999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39.7168169</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ChIJ0asfdEwrwYkRCQ6er149IHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PATEL BABUBHAI S DR &amp; ANSUYA B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20 EISENHOWER LANE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>-74.95690499999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>39.7096094</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ChIJF5NL7DcrwYkRdBHMMKZ5ucI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PATEL NIMISHA K</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>115 EASTMONT LANE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>-74.95416519999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>39.7115455</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ChIJpxz5lUcrwYkRXbAYJOfx7aI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PATEL RAHI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>63 VILLANOVA COURT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>-74.95065339999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>39.7058673</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ChIJW0z-SDkrwYkRkjQUwhwA9Mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TAILOR RUCHI &amp; MISTRY SMITKUMAR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>24 SOUTH CENTRAL AVENUE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>-74.9151912</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39.7064447</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ChIJn5xtNZ8rwYkRvCpvfDTubMo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SHAH RAKESH &amp; RAHKI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>120 BLUE MEADOW LANE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>-74.912987</v>
+      </c>
+      <c r="G33" t="n">
+        <v>39.7002772</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ChIJSYYHj6MrwYkReYVkhQ3wAYo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAREKH SUJESH &amp; PRINCY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>116 CHRISTMAS TREE COURT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>-74.90249399999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.70547090000001</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ChIJX76xz5UrwYkR2yyg-GrfzYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PATEL MONISH &amp; HEMANDRI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SOUTH ROUTE 73</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>-74.89734180000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>39.707206</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ChIJ4cDPS-srwYkR899MDlPuTuU</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PATEL RITAL &amp; JALPA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>31 SUMMER DRIVE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>-74.88357909999999</v>
+      </c>
+      <c r="G36" t="n">
+        <v>39.7132971</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ChIJa1u7-forwYkRNdqvQPidJes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PATEL UMESH &amp; NEELA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>242 PUMP BRANCH ROAD</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>-74.8650993</v>
+      </c>
+      <c r="G37" t="n">
+        <v>39.7210835</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ChIJf_LyAK0uwYkR4NimpVp963Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PATEL TABITHA C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>25 BUCKINGHAM DRIVE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>-74.901358</v>
+      </c>
+      <c r="G38" t="n">
+        <v>39.7314492</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ChIJsdfwTnIswYkRyZi9GedACuU</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PATEL PRAVINCHANDRA P &amp; TARAMATI P</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>188 WHITE CEDAR DRIVE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>-74.91375189999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>39.7235492</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ChIJX79_PocrwYkRusGaE-riH1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LAKHANI AKHTER</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>87 WOODHAVEN WAY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>-74.9908616</v>
+      </c>
+      <c r="G40" t="n">
+        <v>39.7134332</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ChIJQWMHJ8DUxokRjPHgkOknWFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PATEL MONISH &amp; HERMANDRI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>102 HUNTINGTON DRIVE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Winslow Township</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>-74.8618381</v>
+      </c>
+      <c r="G41" t="n">
+        <v>39.626652</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ChIJiyZfGhDWwIkR-5AfbqUDsJk</t>
         </is>
       </c>
     </row>
